--- a/university_statistics_report.xlsx
+++ b/university_statistics_report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>Профиль обучения</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t xml:space="preserve">ИТОГО </t>
+  </si>
+  <si>
+    <t>H/Д</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -202,11 +205,11 @@
       <c r="A3" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="B3" t="n" s="3">
-        <v>6.5</v>
+      <c r="B3" t="s" s="3">
+        <v>6</v>
       </c>
       <c r="C3" t="n" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D3" t="n" s="3">
         <v>1.0</v>
@@ -219,11 +222,11 @@
       <c r="A4" t="s" s="2">
         <v>10</v>
       </c>
-      <c r="B4" t="n" s="3">
-        <v>5.8</v>
+      <c r="B4" t="s" s="3">
+        <v>6</v>
       </c>
       <c r="C4" t="n" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="D4" t="n" s="3">
         <v>1.0</v>
@@ -236,17 +239,17 @@
       <c r="A5" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B5" t="n" s="3">
-        <v>6.03</v>
+      <c r="B5" t="s" s="3">
+        <v>13</v>
       </c>
       <c r="C5" t="n" s="3">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="D5" t="n" s="3">
         <v>3.0</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
